--- a/artfynd/A 43914-2023 artfynd.xlsx
+++ b/artfynd/A 43914-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43914-2023 artfynd.xlsx
+++ b/artfynd/A 43914-2023 artfynd.xlsx
@@ -1020,12 +1020,7 @@
         <v>95715073</v>
       </c>
       <c r="B5" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,19 +1046,25 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Finspång, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540633.0855649395</v>
+        <v>540633</v>
       </c>
       <c r="R5" t="n">
-        <v>6502373.726595663</v>
+        <v>6502373</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1093,27 +1094,18 @@
           <t>2021-08-25</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-08-25</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43914-2023 artfynd.xlsx
+++ b/artfynd/A 43914-2023 artfynd.xlsx
@@ -1020,7 +1020,7 @@
         <v>95715073</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
